--- a/artfynd/A 31468-2023 artfynd.xlsx
+++ b/artfynd/A 31468-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546876</v>
       </c>
       <c r="B2" t="n">
-        <v>56592</v>
+        <v>56596</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>102613</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 31468-2023 artfynd.xlsx
+++ b/artfynd/A 31468-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546876</v>
       </c>
       <c r="B2" t="n">
-        <v>56596</v>
+        <v>56597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31468-2023 artfynd.xlsx
+++ b/artfynd/A 31468-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122546876</v>
       </c>
       <c r="B2" t="n">
-        <v>56597</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
